--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486789_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486789_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1638</v>
+        <v>7.143</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0617</v>
+        <v>6.1651</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1021</v>
+        <v>0.9779</v>
       </c>
       <c r="G2" t="n">
         <v>2.3952</v>
@@ -610,13 +610,13 @@
         <v>2.1239</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1655</v>
+        <v>-0.1862</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1925</v>
+        <v>0.2959</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.358</v>
+        <v>-0.4821</v>
       </c>
       <c r="V2" t="n">
         <v>3.9687</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. VALVERDE SASTRE</t>
+          <t>J. JIMENEZ LAHOZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4313</v>
+        <v>3.2388</v>
       </c>
       <c r="E3" t="n">
-        <v>1.635</v>
+        <v>3.0054</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7964</v>
+        <v>0.2334</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1446</v>
+        <v>1.487</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.9313</v>
+        <v>-1.6825</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7867</v>
+        <v>3.1695</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5323</v>
+        <v>2.3021</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.2409</v>
+        <v>-0.0265</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7732</v>
+        <v>2.3286</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6768999999999999</v>
+        <v>-0.8151</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6904</v>
+        <v>-1.656</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0135</v>
+        <v>0.8409</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3862</v>
+        <v>0.1931</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9654</v>
+        <v>-1.1585</v>
       </c>
       <c r="R3" t="n">
         <v>1.3515</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1898</v>
+        <v>-0.2828</v>
       </c>
       <c r="T3" t="n">
-        <v>2.0681</v>
+        <v>0.0202</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1217</v>
+        <v>-0.303</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.8415</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.8415</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. JIMENEZ LAHOZ</t>
+          <t>J. VALVERDE SASTRE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.159</v>
+        <v>1.1654</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0746</v>
+        <v>0.3939</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0844</v>
+        <v>0.7715</v>
       </c>
       <c r="G4" t="n">
-        <v>1.487</v>
+        <v>-0.1446</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.6825</v>
+        <v>-0.9313</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1695</v>
+        <v>0.7867</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3021</v>
+        <v>0.5323</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0265</v>
+        <v>-0.2409</v>
       </c>
       <c r="L4" t="n">
-        <v>2.3286</v>
+        <v>0.7732</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8151</v>
+        <v>-0.6768999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.656</v>
+        <v>-0.6904</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8409</v>
+        <v>0.0135</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1931</v>
+        <v>0.3862</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1585</v>
+        <v>-0.9654</v>
       </c>
       <c r="R4" t="n">
         <v>1.3515</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3626</v>
+        <v>0.9239000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9106</v>
+        <v>0.827</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.452</v>
+        <v>0.0969</v>
       </c>
       <c r="V4" t="n">
-        <v>1.8415</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.8415</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6644</v>
+        <v>1.0687</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0905</v>
+        <v>2.47</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.4261</v>
+        <v>-1.4012</v>
       </c>
       <c r="G5" t="n">
         <v>2.1629</v>
@@ -844,13 +844,13 @@
         <v>1.7377</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0921</v>
+        <v>0.4964</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0752</v>
+        <v>0.4546</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0169</v>
+        <v>0.0417</v>
       </c>
       <c r="V5" t="n">
         <v>-2.1698</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0385</v>
+        <v>-0.5491</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1994</v>
+        <v>-0.2143</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1609</v>
+        <v>-0.3348</v>
       </c>
       <c r="G6" t="n">
         <v>-0.9214</v>
@@ -922,13 +922,13 @@
         <v>0.7723</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3806</v>
+        <v>-0.2069</v>
       </c>
       <c r="T6" t="n">
-        <v>0.496</v>
+        <v>0.0824</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1154</v>
+        <v>-0.2892</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. MARTÍNEZ LAGO</t>
+          <t>M. YOUNG MEDIERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2573</v>
+        <v>-2.2662</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0417</v>
+        <v>-1.5067</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2156</v>
+        <v>-0.7595</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.8902</v>
+        <v>-1.218</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.6619</v>
+        <v>-4.1795</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2283</v>
+        <v>2.9615</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.3449</v>
+        <v>-0.5962</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.3856</v>
+        <v>-1.9029</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0407</v>
+        <v>1.3067</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5453</v>
+        <v>-0.6219</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2763</v>
+        <v>-2.2766</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.269</v>
+        <v>1.6548</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.5792</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8606</v>
+        <v>-0.662</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3032</v>
+        <v>0.0548</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5574</v>
+        <v>-0.7168</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. YOUNG MEDIERO</t>
+          <t>A. MARTÍNEZ LAGO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4152</v>
+        <v>-2.6628</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5067</v>
+        <v>-1.2485</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9085</v>
+        <v>-1.4142</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.218</v>
+        <v>-1.8902</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.1795</v>
+        <v>-1.6619</v>
       </c>
       <c r="I8" t="n">
-        <v>2.9615</v>
+        <v>-0.2283</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5962</v>
+        <v>-1.3449</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.9029</v>
+        <v>-1.3856</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3067</v>
+        <v>0.0407</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6219</v>
+        <v>-0.5453</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.2766</v>
+        <v>-0.2763</v>
       </c>
       <c r="O8" t="n">
-        <v>1.6548</v>
+        <v>-0.269</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3862</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5792</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8110000000000001</v>
+        <v>0.4551</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0548</v>
+        <v>0.0964</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8658</v>
+        <v>0.3587</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4931</v>
+        <v>-2.9304</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6716</v>
+        <v>-1.2579</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8216</v>
+        <v>-1.6726</v>
       </c>
       <c r="G9" t="n">
         <v>1.796</v>
@@ -1156,13 +1156,13 @@
         <v>0.9654</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.142</v>
+        <v>-0.5793</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5518</v>
+        <v>-0.1381</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-0.4412</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2856</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.809</v>
+        <v>-3.9939</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.353</v>
+        <v>-4.8359</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5439000000000001</v>
+        <v>0.8419</v>
       </c>
       <c r="G10" t="n">
         <v>-3.5748</v>
@@ -1234,13 +1234,13 @@
         <v>0.7723</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3461</v>
+        <v>-0.531</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7174</v>
+        <v>-0.2003</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6287</v>
+        <v>-0.3307</v>
       </c>
       <c r="V10" t="n">
         <v>1.2703</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.2337</v>
+        <v>-4.9649</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.791</v>
+        <v>-2.2739</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4427</v>
+        <v>-2.691</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6087</v>
@@ -1312,13 +1312,13 @@
         <v>0.9654</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5794</v>
+        <v>0.8481</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2211</v>
+        <v>0.296</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8004</v>
+        <v>0.5521</v>
       </c>
       <c r="V11" t="n">
         <v>-4.0113</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.751300000000001</v>
+        <v>-4.7514</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6972000000000009</v>
+        <v>0.6972000000000018</v>
       </c>
       <c r="F12" t="n">
         <v>-5.448600000000001</v>
@@ -1369,13 +1369,13 @@
         <v>-1.3719</v>
       </c>
       <c r="L12" t="n">
-        <v>5.9009</v>
+        <v>5.900899999999998</v>
       </c>
       <c r="M12" t="n">
         <v>-6.0456</v>
       </c>
       <c r="N12" t="n">
-        <v>-8.283100000000001</v>
+        <v>-8.283099999999999</v>
       </c>
       <c r="O12" t="n">
         <v>2.2376</v>
@@ -1396,13 +1396,13 @@
         <v>1.7889</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.5137</v>
+        <v>-1.5136</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6139000000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>7.894700000000001</v>
+        <v>7.894699999999999</v>
       </c>
       <c r="X12" t="n">
         <v>-8.508599999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.8625</v>
+        <v>11.6872</v>
       </c>
       <c r="E13" t="n">
-        <v>11.0612</v>
+        <v>11.4749</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1987</v>
+        <v>0.2124</v>
       </c>
       <c r="G13" t="n">
         <v>5.7421</v>
@@ -1468,13 +1468,13 @@
         <v>2.1239</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9488</v>
+        <v>-0.1241</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1659</v>
+        <v>0.2478</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7829</v>
+        <v>-0.3719</v>
       </c>
       <c r="V13" t="n">
         <v>4.9108</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4333</v>
+        <v>1.4251</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0497</v>
+        <v>3.3257</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6164</v>
+        <v>-1.9006</v>
       </c>
       <c r="G14" t="n">
         <v>2.2284</v>
@@ -1546,13 +1546,13 @@
         <v>0.9654</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9806</v>
+        <v>0.9724</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5717</v>
+        <v>0.8477</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4089</v>
+        <v>0.1246</v>
       </c>
       <c r="V14" t="n">
         <v>-2.741</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8202</v>
+        <v>0.7786999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5516</v>
+        <v>0.7584</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2686</v>
+        <v>0.0203</v>
       </c>
       <c r="G15" t="n">
         <v>-1.5661</v>
@@ -1624,13 +1624,13 @@
         <v>0.9654</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1932</v>
+        <v>0.1517</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3311</v>
+        <v>-0.1242</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5243</v>
+        <v>0.276</v>
       </c>
       <c r="V15" t="n">
         <v>1.2277</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. FORTES SILVA</t>
+          <t>P. BALLESPIN DE LA PEÑA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2509</v>
+        <v>0.0045</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6538</v>
+        <v>-1.1458</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9046999999999999</v>
+        <v>1.1503</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1212</v>
+        <v>-0.1229</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1936</v>
+        <v>0.6344</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-0.7572</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1941</v>
+        <v>0.1065</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3568</v>
+        <v>-0.1921</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1628</v>
+        <v>0.2986</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3153</v>
+        <v>-0.2294</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5505</v>
+        <v>0.8264</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2352</v>
+        <v>-1.0558</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1931</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9308</v>
+        <v>-2.8962</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7377</v>
+        <v>2.1239</v>
       </c>
       <c r="S16" t="n">
-        <v>0.651</v>
+        <v>-0.6136</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1854</v>
+        <v>0.1306</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5344</v>
+        <v>-0.7442</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3282</v>
+        <v>1.5133</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2856</v>
+        <v>1.5133</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. BARBEITO RUIZ</t>
+          <t>A. FORTES SILVA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1551</v>
+        <v>-0.2069</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5656</v>
+        <v>-1.2744</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4105</v>
+        <v>1.0674</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1245</v>
+        <v>0.1212</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6072</v>
+        <v>0.1936</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.7317</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7308</v>
+        <v>-0.1941</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6075</v>
+        <v>-0.3568</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.3383</v>
+        <v>0.1628</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3937</v>
+        <v>0.3153</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0003</v>
+        <v>0.5505</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3934</v>
+        <v>-0.2352</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9654</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9654</v>
+        <v>1.7377</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6178</v>
+        <v>0.1932</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1652</v>
+        <v>0.5649</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4526</v>
+        <v>-0.3717</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6138</v>
+        <v>-0.3282</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X17" t="n">
         <v>-0.6138</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3761</v>
+        <v>-0.5581</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1999</v>
+        <v>-0.0069</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.576</v>
+        <v>-0.5511</v>
       </c>
       <c r="G18" t="n">
         <v>0.5578</v>
@@ -1858,13 +1858,13 @@
         <v>0.5792</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3751</v>
+        <v>0.193</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2204</v>
+        <v>0.0135</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1547</v>
+        <v>0.1795</v>
       </c>
       <c r="V18" t="n">
         <v>0.0426</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. BALLESPIN DE LA PEÑA</t>
+          <t>A. BARBEITO RUIZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3622</v>
+        <v>-0.7178</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0766</v>
+        <v>-0.9792999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7144</v>
+        <v>0.2615</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1229</v>
+        <v>-1.1245</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6344</v>
+        <v>0.6072</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7572</v>
+        <v>-1.7317</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1065</v>
+        <v>-0.7308</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1921</v>
+        <v>0.6075</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2986</v>
+        <v>-1.3383</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2294</v>
+        <v>-0.3937</v>
       </c>
       <c r="N19" t="n">
-        <v>0.8264</v>
+        <v>-0.0003</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0558</v>
+        <v>-0.3934</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7723</v>
+        <v>0.9654</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.8962</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1239</v>
+        <v>0.9654</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.9803</v>
+        <v>0.0551</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8002</v>
+        <v>-0.2485</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.1801</v>
+        <v>0.3036</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5133</v>
+        <v>-0.6138</v>
       </c>
       <c r="W19" t="n">
-        <v>1.5133</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3191</v>
+        <v>-2.0874</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5281</v>
+        <v>-0.3213</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7909</v>
+        <v>-1.7661</v>
       </c>
       <c r="G20" t="n">
         <v>0.4507</v>
@@ -2014,13 +2014,13 @@
         <v>0.7723</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1213</v>
+        <v>0.1103</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2759</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1546</v>
+        <v>0.1794</v>
       </c>
       <c r="V20" t="n">
         <v>-2.4554</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.505</v>
+        <v>-2.3174</v>
       </c>
       <c r="E21" t="n">
         <v>-2.9062</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4012</v>
+        <v>0.5888</v>
       </c>
       <c r="G21" t="n">
         <v>-2.6442</v>
@@ -2092,13 +2092,13 @@
         <v>2.1239</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0771</v>
+        <v>0.1104</v>
       </c>
       <c r="T21" t="n">
         <v>0.7167</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7938</v>
+        <v>-0.6062</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9421</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8982</v>
+        <v>-2.5672</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.6835</v>
+        <v>-3.4767</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7854</v>
+        <v>0.9095</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1259</v>
@@ -2170,13 +2170,13 @@
         <v>1.1585</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9653</v>
+        <v>-0.6343</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7725</v>
+        <v>-0.5657</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1928</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>4.751199999999999</v>
+        <v>5.440700000000003</v>
       </c>
       <c r="E23" t="n">
-        <v>5.448599999999999</v>
+        <v>5.448399999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6971999999999999</v>
+        <v>-0.007600000000000051</v>
       </c>
       <c r="G23" t="n">
-        <v>1.516599999999999</v>
+        <v>1.5166</v>
       </c>
       <c r="H23" t="n">
         <v>9.655099999999999</v>
@@ -2248,22 +2248,22 @@
         <v>13.5156</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2750999999999997</v>
+        <v>0.4141</v>
       </c>
       <c r="T23" t="n">
-        <v>1.5138</v>
+        <v>1.5137</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.7889</v>
+        <v>-1.0995</v>
       </c>
       <c r="V23" t="n">
         <v>0.6139</v>
       </c>
       <c r="W23" t="n">
-        <v>8.5085</v>
+        <v>8.508500000000002</v>
       </c>
       <c r="X23" t="n">
-        <v>-7.8947</v>
+        <v>-7.894699999999999</v>
       </c>
     </row>
   </sheetData>
